--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91615</v>
+        <v>91617</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91619</v>
+        <v>91621</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91621</v>
+        <v>91623</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 30799-2025 artfynd.xlsx
+++ b/artfynd/A 30799-2025 artfynd.xlsx
@@ -1893,7 +1893,7 @@
         <v>129066767</v>
       </c>
       <c r="B13" t="n">
-        <v>91623</v>
+        <v>91625</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
